--- a/output/pdf_financials_xlsx/LBS.PR.A.xlsx
+++ b/output/pdf_financials_xlsx/LBS.PR.A.xlsx
@@ -723,10 +723,10 @@
         <v>3.48157</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>4.054756</v>
+        <v>6.27534</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>4.42972</v>
+        <v>10.929715</v>
       </c>
     </row>
     <row r="11">
@@ -771,10 +771,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.007993999999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.001082</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>0</v>
@@ -786,7 +786,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.008255</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0</v>
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-96.466814</v>
+        <v>-96.474808</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>62.48854</v>
+        <v>62.487458</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>14.550831</v>
@@ -1343,7 +1343,7 @@
         <v>29.887023</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>57.045717</v>
+        <v>57.037462</v>
       </c>
       <c r="H27" s="1" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-96.466814</v>
+        <v>-96.474808</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>62.48854</v>
+        <v>62.487458</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>14.550831</v>
@@ -1409,7 +1409,7 @@
         <v>29.887023</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>57.045717</v>
+        <v>57.037462</v>
       </c>
       <c r="H29" s="1" t="inlineStr">
         <is>
@@ -1583,10 +1583,10 @@
         <v>0</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>2.983992</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.941467</v>
       </c>
     </row>
     <row r="35">
@@ -1645,10 +1645,10 @@
         <v>1.152932</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>2.983992</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>2.941467</v>
       </c>
     </row>
     <row r="37">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -17948,7 +17948,7 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -18314,7 +18314,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E255" s="5" t="n">

--- a/output/pdf_financials_xlsx/LBS.PR.A.xlsx
+++ b/output/pdf_financials_xlsx/LBS.PR.A.xlsx
@@ -4172,19 +4172,19 @@
         </is>
       </c>
       <c r="B115" s="3" t="n">
-        <v>0</v>
+        <v>23.27858</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>61.342784</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>16.030881</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>19.116617</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>33.002922</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -12992,7 +12992,11 @@
           <t>Proceeds from sale of investments (note 9)</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>
@@ -16206,7 +16210,11 @@
           <t>Proceeds from sale of investments (note 8)</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E215" s="5" t="n">
         <v>23.27858</v>
       </c>
@@ -18004,7 +18012,11 @@
           <t>Net investment income (loss) before distributions on Preferred shares</t>
         </is>
       </c>
-      <c r="D249" t="inlineStr"/>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E249" t="inlineStr">
         <is>
           <t>-</t>
@@ -18058,7 +18070,11 @@
           <t>Distributions on Preferred shares (note 6)</t>
         </is>
       </c>
-      <c r="D250" t="inlineStr"/>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E250" s="5" t="n">
         <v>-5.94656</v>
       </c>
@@ -19328,7 +19344,11 @@
           <t>Distributions on Preferred shares (note 7)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>PreferredStockDividends</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
